--- a/data/england/p3_data_preparation/select_data/df_fs.xlsx
+++ b/data/england/p3_data_preparation/select_data/df_fs.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,19 +462,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-1.020942099126798</v>
+        <v>-0.9547232039327125</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.6693845088215091</v>
+        <v>-0.6411730942432816</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2888356434393501</v>
+        <v>-1.710263137648707</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.401490964508957</v>
+        <v>-3.306159435824701</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1459794163521777</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -484,19 +484,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.9421192512394216</v>
+        <v>-0.8499857138856807</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.5453968034192697</v>
+        <v>-0.5024657685774861</v>
       </c>
       <c r="D3" t="n">
-        <v>-1.44417821719675</v>
+        <v>-0.2631174057921088</v>
       </c>
       <c r="E3" t="n">
-        <v>-2.931694271855442</v>
+        <v>-1.615568888255276</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01661228085750334</v>
+        <v>0.1123858273286728</v>
       </c>
     </row>
     <row r="4">
@@ -506,19 +506,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.7121258197540563</v>
+        <v>-0.6223242853764026</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.6574240977380452</v>
+        <v>-0.6323492201907045</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.4043699008150901</v>
+        <v>0.3946761086881632</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.773919818307192</v>
+        <v>-0.8599973968789441</v>
       </c>
       <c r="F4" t="n">
-        <v>0.114493368870689</v>
+        <v>0.1626141497846169</v>
       </c>
     </row>
     <row r="5">
@@ -528,591 +528,1669 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1434520158954682</v>
+        <v>0.01532442818758245</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.9390200127096932</v>
+        <v>-1.464394455134429</v>
       </c>
       <c r="D5" t="n">
-        <v>1.44417821719675</v>
+        <v>1.666410236683356</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6486102203825254</v>
+        <v>0.2173402097365094</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3192999917883645</v>
+        <v>0.2342326019319118</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_90_matches_expected_goals_(xg)</t>
+          <t>dif_mean_last_30_matches_expected_goals_(xg)</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.002241572046442857</v>
+        <v>-0.7408453280296109</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.6497671713071596</v>
+        <v>-1.048077810203822</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.17330138606361</v>
+        <v>0.8770580193070293</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.8208269853243267</v>
+        <v>-0.9118651189264034</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1950701713593133</v>
+        <v>0.1591661257421673</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_90_matches_expected_points</t>
+          <t>dif_mean_last_30_matches_expected_goals_(xg)_against</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.0657093250132174</v>
+        <v>-0.6034003849693501</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.6966443968365</v>
+        <v>-1.17829726680628</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.32864395982101</v>
+        <v>-0.2192645048267573</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.090997681670728</v>
+        <v>-2.000962156602387</v>
       </c>
       <c r="F7" t="n">
-        <v>0.08768682969045159</v>
+        <v>0.08676593883919652</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_90_matches_shots_on_goal</t>
+          <t>dif_mean_last_180_matches_expected_goals_(xg)</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9299394061432701</v>
+        <v>0.3966198275113559</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7870185239781671</v>
+        <v>-0.8691192771753573</v>
       </c>
       <c r="D8" t="n">
-        <v>1.21310970244527</v>
+        <v>1.359439929925895</v>
       </c>
       <c r="E8" t="n">
-        <v>2.930067632566708</v>
+        <v>0.8869404802618941</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5121799893353378</v>
+        <v>0.2787457931896598</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_90_matches_goal_attempts</t>
+          <t>dif_mean_last_180_matches_expected_goals_(xg)_against</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.428013624284425</v>
+        <v>-0.5202256131490173</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5624556606008659</v>
+        <v>-1.11979054204874</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.05776712868787001</v>
+        <v>-0.3946761086881632</v>
       </c>
       <c r="E9" t="n">
-        <v>1.932702156197421</v>
+        <v>-2.03469226388592</v>
       </c>
       <c r="F9" t="n">
-        <v>0.427860269138863</v>
+        <v>0.08452365372859136</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_90_matches_goals</t>
+          <t>dif_mean_last_30_matches_expected_points</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.7136188506251436</v>
+        <v>-0.2073979775094229</v>
       </c>
       <c r="C10" t="n">
-        <v>0.336218542967671</v>
+        <v>-0.9583672746464328</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.09757544506953</v>
+        <v>-0.3508232077228117</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.04773805147671584</v>
+        <v>-1.516588459878667</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2604290033356524</v>
+        <v>0.1189657749975183</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_90_matches_points</t>
+          <t>dif_mean_last_180_matches_expected_points</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.5242166706954989</v>
+        <v>0.3233455653178543</v>
       </c>
       <c r="C11" t="n">
-        <v>0.6711867861609737</v>
+        <v>-1.015582908420469</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5199041581908301</v>
+        <v>0.6139406135149205</v>
       </c>
       <c r="E11" t="n">
-        <v>1.715307615047303</v>
+        <v>-0.07829672958769451</v>
       </c>
       <c r="F11" t="n">
-        <v>0.4094812021706056</v>
+        <v>0.2145794682605828</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_90_matches_goal_ratio</t>
+          <t>dif_mean_last_30_matches_shots_on_goal</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.2052325223736394</v>
+        <v>0.2014678667381511</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.1888087142701523</v>
+        <v>0.5164666281068614</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.9820411876937902</v>
+        <v>0.7893522173763263</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.9656173795903031</v>
+        <v>1.507286712221339</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1828292367963006</v>
+        <v>0.3199847109212307</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_90_matches_PPS</t>
+          <t>dif_mean_last_30_matches_shots_on_goal_against</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1571275816709735</v>
+        <v>-0.8430267661991071</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.3341920978777195</v>
+        <v>-0.4917523967346178</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.8665069303180502</v>
+        <v>1.227881227029841</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.043571446524796</v>
+        <v>-0.106897935903884</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1762388090465637</v>
+        <v>0.2126781384329292</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_90_matches_attacks</t>
+          <t>dif_mean_last_180_matches_shots_on_goal_against</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.161001745694866</v>
+        <v>0.03302609143093158</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2566472851714623</v>
+        <v>-0.2668257007171683</v>
       </c>
       <c r="D14" t="n">
-        <v>0.05776712868787001</v>
+        <v>-0.04385290096535147</v>
       </c>
       <c r="E14" t="n">
-        <v>1.475416159554198</v>
+        <v>-0.2776525102515882</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3892001909626198</v>
+        <v>0.2013268422034475</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_90_matches_dangerous_attacks</t>
+          <t>dif_mean_last_30_matches_goal_attempts</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.659110506926845</v>
+        <v>0.3006255964177197</v>
       </c>
       <c r="C15" t="n">
-        <v>0.159170072282552</v>
+        <v>0.4316823776021747</v>
       </c>
       <c r="D15" t="n">
-        <v>1.55971247457249</v>
+        <v>-1.315587028960544</v>
       </c>
       <c r="E15" t="n">
-        <v>3.377993053781887</v>
+        <v>-0.5832790549406494</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5500487015382531</v>
+        <v>0.1810096269393102</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_90_matches_dead_balls</t>
+          <t>dif_mean_last_30_matches_goal_attempts_against</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.03967921215736623</v>
+        <v>-0.45500233495995</v>
       </c>
       <c r="C16" t="n">
-        <v>0.3899757710687446</v>
+        <v>-0.3520647397154854</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.67524673194823</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.24559174872212</v>
+        <v>-0.8070670746754354</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1591595178951439</v>
+        <v>0.1661328125738812</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_90_matches_yellow_cards</t>
+          <t>dif_mean_last_180_matches_goal_attempts</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.8095120156379821</v>
+        <v>2.076757868836596</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.6412474954941555</v>
+        <v>1.439701427808498</v>
       </c>
       <c r="D17" t="n">
-        <v>0.17330138606361</v>
+        <v>0.6577935144802719</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.277458125068528</v>
+        <v>4.174252811125366</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1564654563892393</v>
+        <v>0.4972773096014818</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_90_matches_red_cards</t>
+          <t>dif_mean_last_180_matches_goal_attempts_against</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-1.069742650527046</v>
+        <v>0.9527111662789531</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.8677716410552433</v>
+        <v>0.1418864936298981</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2888356434393501</v>
+        <v>-0.3069703067574602</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.22634993502164</v>
+        <v>0.7876273531513909</v>
       </c>
       <c r="F18" t="n">
-        <v>0.07624381867701892</v>
+        <v>0.2721437286205904</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_90_matches_defensive_actions</t>
+          <t>dif_mean_last_30_matches_goals</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-1.067013359038838</v>
+        <v>-0.1879499952238104</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.3591801604507672</v>
+        <v>-0.3158581524226666</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.6354384155665701</v>
+        <v>-0.570087712549569</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.061631935056175</v>
+        <v>-1.073895860196046</v>
       </c>
       <c r="F19" t="n">
-        <v>0.09016948183409047</v>
+        <v>0.1483947660321255</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_90_matches_PPDA</t>
+          <t>dif_mean_last_30_matches_goals_against</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.170592507949824</v>
+        <v>-0.7869627607828995</v>
       </c>
       <c r="C20" t="n">
-        <v>0.7379813491622345</v>
+        <v>-0.3400659821631752</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9820411876937902</v>
+        <v>0.9647638212377322</v>
       </c>
       <c r="E20" t="n">
-        <v>2.890615044805849</v>
+        <v>-0.1622649217083426</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5088445709357233</v>
+        <v>0.2089974929240122</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_90_matches_KGP</t>
+          <t>dif_mean_last_180_matches_goals</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.8016940449302402</v>
+        <v>1.973874152703566</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.3471589070325217</v>
+        <v>0.5669229097257485</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.21310970244527</v>
+        <v>-0.6577935144802719</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.361962654408032</v>
+        <v>1.883003547949043</v>
       </c>
       <c r="F21" t="n">
-        <v>0.06477878722699326</v>
+        <v>0.3449613366839126</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_90_matches_clean_sheet</t>
+          <t>dif_mean_last_180_matches_goals_against</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.1293707138479774</v>
+        <v>0.1912447806651491</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.2762148662769969</v>
+        <v>-0.4182679087910829</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.5199041581908301</v>
+        <v>-0.7454993164109749</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.9254897383158044</v>
+        <v>-0.9725224445369087</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1862217258733513</v>
+        <v>0.1551337929386496</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_90_matches_mean_rat_player_start_against</t>
+          <t>dif_mean_last_30_matches_points_against</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.5062423045212828</v>
+        <v>-0.4012971007369109</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.02255352286015692</v>
+        <v>-0.1356360990071229</v>
       </c>
       <c r="D23" t="n">
-        <v>0.8665069303180502</v>
+        <v>-0.8332051183416778</v>
       </c>
       <c r="E23" t="n">
-        <v>0.3377111029366104</v>
+        <v>-1.370138318085711</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2930158189214624</v>
+        <v>0.1287013791457054</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_hei_player_start</t>
+          <t>dif_mean_last_180_matches_points_against</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.9297781394399681</v>
+        <v>1.125711594520578</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.4618648156307221</v>
+        <v>0.5925459645161659</v>
       </c>
       <c r="D24" t="n">
-        <v>0.7509726729423102</v>
+        <v>-0.9209109202723808</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.64067028212838</v>
+        <v>0.7973466387643636</v>
       </c>
       <c r="F24" t="n">
-        <v>0.210301060301149</v>
+        <v>0.2727898400969784</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>dif_n_player_miss</t>
+          <t>dif_mean_last_30_matches_goal_ratio</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.8207374467313084</v>
+        <v>-0.8345130879805017</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.6969921626891099</v>
+        <v>-0.2635027171906392</v>
       </c>
       <c r="D25" t="n">
-        <v>0.6354384155665701</v>
+        <v>-1.008616722203084</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.8822911938538481</v>
+        <v>-2.106632527374225</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1898738366273619</v>
+        <v>0.07974126213057861</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_rat_player_start</t>
+          <t>dif_mean_last_30_matches_goal_ratio_against</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.501371631215938</v>
+        <v>-0.7640540658132827</v>
       </c>
       <c r="C26" t="n">
-        <v>4.523568479776435</v>
+        <v>-0.3647350827944963</v>
       </c>
       <c r="D26" t="n">
-        <v>1.67524673194823</v>
+        <v>-0.08770580193070293</v>
       </c>
       <c r="E26" t="n">
-        <v>8.700186842940603</v>
+        <v>-1.216494950538482</v>
       </c>
       <c r="F26" t="n">
-        <v>1</v>
+        <v>0.1389151692323613</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_rat_player_sub</t>
+          <t>dif_mean_last_180_matches_goal_ratio</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.77012961538373</v>
+        <v>0.4804105347224288</v>
       </c>
       <c r="C27" t="n">
-        <v>1.203634743466572</v>
+        <v>-0.2453005313008833</v>
       </c>
       <c r="D27" t="n">
-        <v>1.32864395982101</v>
+        <v>-1.184028326064489</v>
       </c>
       <c r="E27" t="n">
-        <v>4.302408318671311</v>
+        <v>-0.9489183226429441</v>
       </c>
       <c r="F27" t="n">
-        <v>0.6282010321809531</v>
+        <v>0.1567029302860894</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_hei_player_miss</t>
+          <t>dif_mean_last_180_matches_goal_ratio_against</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-1.064355111768095</v>
+        <v>0.946290171819386</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.1197467672214723</v>
+        <v>-0.1625986151399795</v>
       </c>
       <c r="D28" t="n">
-        <v>0.4043699008150901</v>
+        <v>-1.359439929925895</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.7797319781744776</v>
+        <v>-0.575748373246489</v>
       </c>
       <c r="F28" t="n">
-        <v>0.198544443916813</v>
+        <v>0.1815102460240224</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_hei_player_sub</t>
+          <t>dif_mean_last_30_matches_PPS</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.3268222739394873</v>
+        <v>-0.6432583582209743</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.2292648521717695</v>
+        <v>-0.1494714817440065</v>
       </c>
       <c r="D29" t="n">
-        <v>1.09757544506953</v>
+        <v>-1.447145731856598</v>
       </c>
       <c r="E29" t="n">
-        <v>0.5414883189582735</v>
+        <v>-2.239875571821579</v>
       </c>
       <c r="F29" t="n">
-        <v>0.3102436438707604</v>
+        <v>0.07088362962604569</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_age_player_start</t>
+          <t>dif_mean_last_30_matches_PPS_against</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-1.06878253357084</v>
+        <v>-0.8073241251671476</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.4275264692955011</v>
+        <v>-0.6308265243073349</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.7509726729423102</v>
+        <v>-1.534851533787301</v>
       </c>
       <c r="E30" t="n">
-        <v>-2.247281675808652</v>
+        <v>-2.973002183261784</v>
       </c>
       <c r="F30" t="n">
-        <v>0.07447419804325586</v>
+        <v>0.02214738128854554</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_180_matches_PPS</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>1.155818109852838</v>
+      </c>
+      <c r="C31" t="n">
+        <v>-0.2814227448172195</v>
+      </c>
+      <c r="D31" t="n">
+        <v>-1.622557335718004</v>
+      </c>
+      <c r="E31" t="n">
+        <v>-0.7481619706823859</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.1700486624854155</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_180_matches_PPS_against</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>0.4681027591521087</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.1002266810535011</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1.052469623168435</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1.620799063374045</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.3275307009982844</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_30_matches_attacks</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>-0.5043642496106789</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.2711041405627201</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1.49099863282195</v>
+      </c>
+      <c r="E33" t="n">
+        <v>1.257738523773991</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.3033954311235006</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_30_matches_attacks_against</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>-0.005106622079804415</v>
+      </c>
+      <c r="C34" t="n">
+        <v>1.374308292207574</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.9209109202723808</v>
+      </c>
+      <c r="E34" t="n">
+        <v>2.29011259040015</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.3720248303338867</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_180_matches_attacks</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>1.370440376518982</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.4033268101387505</v>
+      </c>
+      <c r="D35" t="n">
+        <v>-0.4385290096535147</v>
+      </c>
+      <c r="E35" t="n">
+        <v>1.335238177004218</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.3085473957186455</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_180_matches_attacks_against</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>1.695085181609654</v>
+      </c>
+      <c r="C36" t="n">
+        <v>1.711522679222056</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.2192645048267573</v>
+      </c>
+      <c r="E36" t="n">
+        <v>3.625872365658467</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.4608224801673118</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_30_matches_dangerous_attacks</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>0.7144444716205154</v>
+      </c>
+      <c r="C37" t="n">
+        <v>1.075699209712377</v>
+      </c>
+      <c r="D37" t="n">
+        <v>1.578704434752653</v>
+      </c>
+      <c r="E37" t="n">
+        <v>3.368848116085545</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.4437362123106071</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_30_matches_dangerous_attacks_against</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>-0.3576067537185661</v>
+      </c>
+      <c r="C38" t="n">
+        <v>-0.1298427650377893</v>
+      </c>
+      <c r="D38" t="n">
+        <v>-0.4823819106188661</v>
+      </c>
+      <c r="E38" t="n">
+        <v>-0.9698314293752215</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.1553126842531284</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_180_matches_dangerous_attacks</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>2.464238913447689</v>
+      </c>
+      <c r="C39" t="n">
+        <v>1.411712843213662</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1.622557335718004</v>
+      </c>
+      <c r="E39" t="n">
+        <v>5.498509092379354</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.5853102386734511</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_180_matches_dangerous_attacks_against</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>1.37488487855617</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.3461085207295337</v>
+      </c>
+      <c r="D40" t="n">
+        <v>-1.052469623168435</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.6685237761172684</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.2642260491670831</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_30_matches_dead_balls</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>-0.9658196539847963</v>
+      </c>
+      <c r="C41" t="n">
+        <v>-0.3544247709634645</v>
+      </c>
+      <c r="D41" t="n">
+        <v>1.271734127995192</v>
+      </c>
+      <c r="E41" t="n">
+        <v>-0.04851029695306841</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.216559588686327</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_30_matches_dead_balls_against</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>-0.3029376660102217</v>
+      </c>
+      <c r="C42" t="n">
+        <v>-0.4590567151588216</v>
+      </c>
+      <c r="D42" t="n">
+        <v>-1.271734127995192</v>
+      </c>
+      <c r="E42" t="n">
+        <v>-2.033728509164236</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0.0845877215017693</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_180_matches_dead_balls</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>-0.8157782196072378</v>
+      </c>
+      <c r="C43" t="n">
+        <v>-0.2560382151722057</v>
+      </c>
+      <c r="D43" t="n">
+        <v>-1.096322524133787</v>
+      </c>
+      <c r="E43" t="n">
+        <v>-2.16813895891323</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0.07565248309151226</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_180_matches_dead_balls_against</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>0.7917244528214882</v>
+      </c>
+      <c r="C44" t="n">
+        <v>-0.180440751782187</v>
+      </c>
+      <c r="D44" t="n">
+        <v>-1.227881227029841</v>
+      </c>
+      <c r="E44" t="n">
+        <v>-0.6165975259905397</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.1787947062776208</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_30_matches_total_passes_against</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>-0.6090245925340899</v>
+      </c>
+      <c r="C45" t="n">
+        <v>-0.02655768646303233</v>
+      </c>
+      <c r="D45" t="n">
+        <v>-0.9647638212377322</v>
+      </c>
+      <c r="E45" t="n">
+        <v>-1.600346100234854</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.1133977965653302</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_180_matches_total_passes</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>1.817804064708669</v>
+      </c>
+      <c r="C46" t="n">
+        <v>1.057881404780293</v>
+      </c>
+      <c r="D46" t="n">
+        <v>-0.8770580193070293</v>
+      </c>
+      <c r="E46" t="n">
+        <v>1.998627450181933</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.3526476968910575</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_180_matches_total_passes_against</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>0.8874709718624113</v>
+      </c>
+      <c r="C47" t="n">
+        <v>0.4797759588217048</v>
+      </c>
+      <c r="D47" t="n">
+        <v>-0.5262348115842176</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.8410121190998986</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0.2756926015848315</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_30_matches_yellow_cards</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>-0.8483606049523138</v>
+      </c>
+      <c r="C48" t="n">
+        <v>-0.5465569028281625</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0.08770580193070293</v>
+      </c>
+      <c r="E48" t="n">
+        <v>-1.307211705849773</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0.1328845679061619</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_30_matches_yellow_cards_against</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>-0.8767051392475192</v>
+      </c>
+      <c r="C49" t="n">
+        <v>-0.3527025897389885</v>
+      </c>
+      <c r="D49" t="n">
+        <v>0.7016464154456235</v>
+      </c>
+      <c r="E49" t="n">
+        <v>-0.5277613135408843</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0.1847002942671279</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_180_matches_yellow_cards</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>-0.290616502605764</v>
+      </c>
+      <c r="C50" t="n">
+        <v>-0.3453507235700294</v>
+      </c>
+      <c r="D50" t="n">
+        <v>-0.6139406135149205</v>
+      </c>
+      <c r="E50" t="n">
+        <v>-1.249907839690714</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0.1366939719139369</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_180_matches_yellow_cards_against</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>-0.8066931389875986</v>
+      </c>
+      <c r="C51" t="n">
+        <v>-0.1717631442125289</v>
+      </c>
+      <c r="D51" t="n">
+        <v>-0.7016464154456235</v>
+      </c>
+      <c r="E51" t="n">
+        <v>-1.680102698645751</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0.1080957964386785</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_180_matches_red_cards</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>-0.8881448047992905</v>
+      </c>
+      <c r="C52" t="n">
+        <v>-0.7620126485254284</v>
+      </c>
+      <c r="D52" t="n">
+        <v>0.3508232077228117</v>
+      </c>
+      <c r="E52" t="n">
+        <v>-1.299334245601907</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0.1334082398789397</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_30_matches_defensive_actions</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>-0.8151613312196092</v>
+      </c>
+      <c r="C53" t="n">
+        <v>-0.2847194622661427</v>
+      </c>
+      <c r="D53" t="n">
+        <v>-0.7893522173763263</v>
+      </c>
+      <c r="E53" t="n">
+        <v>-1.889233010862078</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0.09419338630647561</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_30_matches_defensive_actions_against</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>-0.6619048403616653</v>
+      </c>
+      <c r="C54" t="n">
+        <v>-0.1678557687707594</v>
+      </c>
+      <c r="D54" t="n">
+        <v>1.184028326064489</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.3542677169320647</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0.243335167424396</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_180_matches_defensive_actions</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>-0.8368347155518383</v>
+      </c>
+      <c r="C55" t="n">
+        <v>-0.4771014981345774</v>
+      </c>
+      <c r="D55" t="n">
+        <v>0.04385290096535147</v>
+      </c>
+      <c r="E55" t="n">
+        <v>-1.270083312721064</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0.1353527617483393</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_180_matches_defensive_actions_against</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>-0.8725521193079113</v>
+      </c>
+      <c r="C56" t="n">
+        <v>-0.3268659138633733</v>
+      </c>
+      <c r="D56" t="n">
+        <v>0.2631174057921088</v>
+      </c>
+      <c r="E56" t="n">
+        <v>-0.9363006273791756</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0.1575417200943245</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_30_matches_PPDA</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>-0.91506890957389</v>
+      </c>
+      <c r="C57" t="n">
+        <v>-0.161409084372014</v>
+      </c>
+      <c r="D57" t="n">
+        <v>0.7454993164109749</v>
+      </c>
+      <c r="E57" t="n">
+        <v>-0.330978677534929</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0.1977818647179045</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_30_matches_PPDA_against</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>0.6153357112873745</v>
+      </c>
+      <c r="C58" t="n">
+        <v>-0.02881054783717926</v>
+      </c>
+      <c r="D58" t="n">
+        <v>-1.403292830891247</v>
+      </c>
+      <c r="E58" t="n">
+        <v>-0.8167676674410517</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0.1654879437467665</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_180_matches_PPDA</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>-0.1742822037655415</v>
+      </c>
+      <c r="C59" t="n">
+        <v>-0.1000656578170891</v>
+      </c>
+      <c r="D59" t="n">
+        <v>0.4385290096535147</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.164181148070884</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0.2306987331699597</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_30_matches_KGP</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>-0.786692744001024</v>
+      </c>
+      <c r="C60" t="n">
+        <v>-0.3458371776937193</v>
+      </c>
+      <c r="D60" t="n">
+        <v>-0.1315587028960544</v>
+      </c>
+      <c r="E60" t="n">
+        <v>-1.264088624590798</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0.1357512721895967</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_30_matches_KGP_against</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>-0.9657294070696262</v>
+      </c>
+      <c r="C61" t="n">
+        <v>-0.1230223219816994</v>
+      </c>
+      <c r="D61" t="n">
+        <v>0.1315587028960544</v>
+      </c>
+      <c r="E61" t="n">
+        <v>-0.9571930261552711</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0.1561528506695499</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_180_matches_KGP</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>-0.5019860078211776</v>
+      </c>
+      <c r="C62" t="n">
+        <v>-0.3293907639122718</v>
+      </c>
+      <c r="D62" t="n">
+        <v>1.315587028960544</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0.4842102572270943</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0.2519733914563724</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_180_matches_KGP_against</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>-0.9188703205775456</v>
+      </c>
+      <c r="C63" t="n">
+        <v>-0.3773288280814854</v>
+      </c>
+      <c r="D63" t="n">
+        <v>1.534851533787301</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0.2386523851282703</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0.2356493769558941</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_30_matches_clean_sheet</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>-0.8705425799810868</v>
+      </c>
+      <c r="C64" t="n">
+        <v>-0.8205676791281408</v>
+      </c>
+      <c r="D64" t="n">
+        <v>0.4823819106188661</v>
+      </c>
+      <c r="E64" t="n">
+        <v>-1.208728348490361</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0.139431471655775</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_30_matches_clean_sheet_against</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>-0.7783253859152827</v>
+      </c>
+      <c r="C65" t="n">
+        <v>-0.8379169668651153</v>
+      </c>
+      <c r="D65" t="n">
+        <v>-0.1754116038614059</v>
+      </c>
+      <c r="E65" t="n">
+        <v>-1.791653956641804</v>
+      </c>
+      <c r="F65" t="n">
+        <v>0.1006801744612193</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_180_matches_clean_sheet</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>0.1198340581879642</v>
+      </c>
+      <c r="C66" t="n">
+        <v>-0.2300759931906388</v>
+      </c>
+      <c r="D66" t="n">
+        <v>-1.49099863282195</v>
+      </c>
+      <c r="E66" t="n">
+        <v>-1.601240567824624</v>
+      </c>
+      <c r="F66" t="n">
+        <v>0.113338334810833</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_180_matches_clean_sheet_against</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>0.689355913683477</v>
+      </c>
+      <c r="C67" t="n">
+        <v>0.1211737845130119</v>
+      </c>
+      <c r="D67" t="n">
+        <v>-1.578704434752653</v>
+      </c>
+      <c r="E67" t="n">
+        <v>-0.7681747365561636</v>
+      </c>
+      <c r="F67" t="n">
+        <v>0.1687182686457639</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_180_matches_mean_rat_player_start_against</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>-0.2468722371820108</v>
+      </c>
+      <c r="C68" t="n">
+        <v>0.02263281383849406</v>
+      </c>
+      <c r="D68" t="n">
+        <v>-1.666410236683356</v>
+      </c>
+      <c r="E68" t="n">
+        <v>-1.890649660026872</v>
+      </c>
+      <c r="F68" t="n">
+        <v>0.09409921135166543</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1" t="inlineStr">
+        <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>-0.5464170920867629</v>
+      </c>
+      <c r="C69" t="n">
+        <v>-0.7663700076405868</v>
+      </c>
+      <c r="D69" t="n">
+        <v>1.008616722203084</v>
+      </c>
+      <c r="E69" t="n">
+        <v>-0.3041703775242659</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0.199564007046989</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>0.7263191983329705</v>
+      </c>
+      <c r="C70" t="n">
+        <v>0.2405964792476131</v>
+      </c>
+      <c r="D70" t="n">
+        <v>-1.140175425099138</v>
+      </c>
+      <c r="E70" t="n">
+        <v>-0.1732597475185544</v>
+      </c>
+      <c r="F70" t="n">
+        <v>0.2082665870303339</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>3.382092535170046</v>
+      </c>
+      <c r="C71" t="n">
+        <v>6.644222821516424</v>
+      </c>
+      <c r="D71" t="n">
+        <v>1.710263137648707</v>
+      </c>
+      <c r="E71" t="n">
+        <v>11.73657849433518</v>
+      </c>
+      <c r="F71" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>-0.76279992045739</v>
+      </c>
+      <c r="C72" t="n">
+        <v>-0.06826966797533131</v>
+      </c>
+      <c r="D72" t="n">
+        <v>1.140175425099138</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0.3091058366664168</v>
+      </c>
+      <c r="F72" t="n">
+        <v>0.240332929369374</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>-0.8897782455658292</v>
+      </c>
+      <c r="C73" t="n">
+        <v>0.2954254737177506</v>
+      </c>
+      <c r="D73" t="n">
+        <v>0.3069703067574602</v>
+      </c>
+      <c r="E73" t="n">
+        <v>-0.2873824650906183</v>
+      </c>
+      <c r="F73" t="n">
+        <v>0.2006800214661453</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>2.362284537122463</v>
+      </c>
+      <c r="C74" t="n">
+        <v>1.637193391712609</v>
+      </c>
+      <c r="D74" t="n">
+        <v>0.1754116038614059</v>
+      </c>
+      <c r="E74" t="n">
+        <v>4.174889532696478</v>
+      </c>
+      <c r="F74" t="n">
+        <v>0.4973196371068913</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_age_player_sub</t>
         </is>
       </c>
-      <c r="B31" t="n">
-        <v>-1.070780373976867</v>
-      </c>
-      <c r="C31" t="n">
-        <v>-0.4976977514772116</v>
-      </c>
-      <c r="D31" t="n">
-        <v>-1.55971247457249</v>
-      </c>
-      <c r="E31" t="n">
-        <v>-3.128190600026569</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0</v>
+      <c r="B75" t="n">
+        <v>-0.9664682300339218</v>
+      </c>
+      <c r="C75" t="n">
+        <v>-0.05552068422530521</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1.096322524133787</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0.07433360987455973</v>
+      </c>
+      <c r="F75" t="n">
+        <v>0.2247259150158799</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>-0.9235018225571925</v>
+      </c>
+      <c r="C76" t="n">
+        <v>-0.1286258529477197</v>
+      </c>
+      <c r="D76" t="n">
+        <v>0.5262348115842176</v>
+      </c>
+      <c r="E76" t="n">
+        <v>-0.5258928639206947</v>
+      </c>
+      <c r="F76" t="n">
+        <v>0.1848245036782647</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_wage_player_sub</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>2.009025423077516</v>
+      </c>
+      <c r="C77" t="n">
+        <v>1.771789542460396</v>
+      </c>
+      <c r="D77" t="n">
+        <v>1.403292830891247</v>
+      </c>
+      <c r="E77" t="n">
+        <v>5.184107796429159</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0.564409701988581</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>-0.3638643911812597</v>
+      </c>
+      <c r="C78" t="n">
+        <v>0.387547491594516</v>
+      </c>
+      <c r="D78" t="n">
+        <v>1.447145731856598</v>
+      </c>
+      <c r="E78" t="n">
+        <v>1.470828832269855</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0.317561090957847</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_value_player_miss</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>0.5771249004661948</v>
+      </c>
+      <c r="C79" t="n">
+        <v>0.1178173408734927</v>
+      </c>
+      <c r="D79" t="n">
+        <v>0.570087712549569</v>
+      </c>
+      <c r="E79" t="n">
+        <v>1.265029953889257</v>
+      </c>
+      <c r="F79" t="n">
+        <v>0.303880145418805</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>-0.9476945483435719</v>
+      </c>
+      <c r="C80" t="n">
+        <v>-0.09682439685715254</v>
+      </c>
+      <c r="D80" t="n">
+        <v>0.8332051183416778</v>
+      </c>
+      <c r="E80" t="n">
+        <v>-0.2113138268590466</v>
+      </c>
+      <c r="F80" t="n">
+        <v>0.2057368561052078</v>
       </c>
     </row>
   </sheetData>
